--- a/data/trans_dic/IP16A05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,54</t>
+          <t>0,0; 30,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,48; 49,8</t>
+          <t>10,79; 50,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,72</t>
+          <t>0,0; 14,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 46,6</t>
+          <t>2,8; 43,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 39,82</t>
+          <t>5,24; 40,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 30,96</t>
+          <t>3,24; 30,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 35,86</t>
+          <t>5,99; 34,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,89</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 26,49</t>
+          <t>4,7; 28,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 34,18</t>
+          <t>9,65; 34,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 22,59</t>
+          <t>4,55; 20,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 29,02</t>
+          <t>2,52; 28,9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,44</t>
+          <t>0,0; 24,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 21,18</t>
+          <t>2,6; 22,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 18,0</t>
+          <t>2,06; 17,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 6,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,35</t>
+          <t>0,0; 16,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 24,09</t>
+          <t>2,61; 23,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,7; 49,84</t>
+          <t>17,3; 51,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 9,19</t>
+          <t>0,83; 9,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 13,72</t>
+          <t>1,55; 13,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 18,18</t>
+          <t>4,09; 18,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 26,76</t>
+          <t>9,78; 26,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,43</t>
+          <t>0,44; 6,11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,89</t>
+          <t>0,0; 23,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,35; 51,43</t>
+          <t>13,29; 52,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 52,13</t>
+          <t>6,98; 54,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,89</t>
+          <t>0,0; 10,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,58</t>
+          <t>0,0; 29,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,85; 34,98</t>
+          <t>6,31; 35,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,94</t>
+          <t>0,0; 32,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,44</t>
+          <t>0,0; 17,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,13</t>
+          <t>0,0; 17,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,84; 36,08</t>
+          <t>13,3; 36,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 35,58</t>
+          <t>7,3; 36,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,53</t>
+          <t>0,0; 9,42</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,79</t>
+          <t>0,0; 22,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 30,88</t>
+          <t>4,37; 32,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 32,13</t>
+          <t>8,16; 33,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 37,23</t>
+          <t>4,16; 38,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 45,43</t>
+          <t>5,61; 42,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 22,57</t>
+          <t>2,64; 22,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,75</t>
+          <t>0,0; 51,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 24,45</t>
+          <t>4,03; 22,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,9; 28,86</t>
+          <t>7,58; 29,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 23,23</t>
+          <t>6,68; 22,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,11</t>
+          <t>0,0; 26,31</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,54; 54,29</t>
+          <t>10,43; 54,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,7</t>
+          <t>0,0; 52,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,07</t>
+          <t>0,0; 40,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,9</t>
+          <t>0,0; 23,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 31,62</t>
+          <t>8,02; 33,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,36</t>
+          <t>0,0; 32,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,63</t>
+          <t>0,0; 17,54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,74</t>
+          <t>0,0; 28,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,73</t>
+          <t>0,0; 47,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,76</t>
+          <t>0,0; 39,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,6</t>
+          <t>0,0; 38,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,52</t>
+          <t>0,0; 35,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,86</t>
+          <t>3,88; 30,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,21</t>
+          <t>0,0; 50,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,4</t>
+          <t>0,0; 27,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 22,5</t>
+          <t>2,65; 22,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,67; 25,49</t>
+          <t>5,01; 25,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,96</t>
+          <t>0,0; 29,73</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,74</t>
+          <t>0,0; 20,85</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 32,74</t>
+          <t>6,09; 29,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 25,34</t>
+          <t>2,6; 24,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,98; 38,67</t>
+          <t>13,44; 38,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,25</t>
+          <t>0,0; 16,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 24,11</t>
+          <t>2,52; 24,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 21,37</t>
+          <t>3,52; 20,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,51; 20,21</t>
+          <t>4,34; 19,04</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,27; 20,33</t>
+          <t>4,81; 20,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,35; 24,95</t>
+          <t>9,29; 24,71</t>
         </is>
       </c>
     </row>
@@ -1696,57 +1697,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,94; 24,83</t>
+          <t>4,94; 27,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,96; 36,69</t>
+          <t>8,57; 37,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,6; 35,77</t>
+          <t>8,34; 34,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,9; 24,69</t>
+          <t>7,0; 25,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,87; 34,0</t>
+          <t>3,46; 33,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,82; 24,88</t>
+          <t>2,74; 23,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,1</t>
+          <t>0,0; 29,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,34; 21,84</t>
+          <t>8,06; 21,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,58; 28,65</t>
+          <t>10,05; 29,36</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,81; 24,18</t>
+          <t>7,6; 23,4</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,51; 13,73</t>
+          <t>5,14; 13,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,88; 23,92</t>
+          <t>12,83; 23,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,52; 16,59</t>
+          <t>7,72; 16,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,64; 14,54</t>
+          <t>4,53; 14,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,49; 15,09</t>
+          <t>6,8; 14,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,82; 18,12</t>
+          <t>8,86; 17,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,73; 18,77</t>
+          <t>8,27; 18,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,11</t>
+          <t>3,17; 9,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,83; 12,52</t>
+          <t>6,87; 12,81</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12,25; 19,17</t>
+          <t>12,25; 19,08</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9,44; 16,06</t>
+          <t>9,47; 16,29</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,64; 10,42</t>
+          <t>4,72; 9,94</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4474</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3148</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6564</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3748</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5261</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3608</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1736; 8133</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2333</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>851; 13183</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>636; 4891</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>584; 5521</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1151; 6607</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2178</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1118; 6729</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3292; 11894</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1605; 7351</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1329; 15233</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1182</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1778</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6673</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1824</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4642</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8451</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2374</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4159</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>610; 5369</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>563; 4897</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4186</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3182</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>651; 5862</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3578; 10555</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>398; 4754</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>568; 4909</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1980; 9126</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4690; 12921</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>492; 6796</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2221</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4159</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8659</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2784</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2064; 8152</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>665; 5232</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1885</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3152</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1408; 7906</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2735</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3507</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3914</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5032; 13950</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1304; 6519</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3602</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2597</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4286</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2783</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2168</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3564</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5638</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6454</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3665</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>844; 6373</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1941; 8018</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>684; 6276</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>855; 6489</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>674; 5659</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5718</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1319; 7379</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2621; 10320</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3300; 10873</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6208</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3974</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1194</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>4671</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1194</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1514; 7850</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3388</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3333</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2865</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2150; 8958</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3764</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3319</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1483</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2224</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3574</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5239</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3637</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2986</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3772</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>702; 5460</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4364</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3699</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>612; 5170</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1456; 7524</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5290</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4439</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>3474</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2958</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7278</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4435</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>5377</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>11713</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1310; 6438</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>691; 6636</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>4003; 11450</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4332</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>640; 6177</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1563; 9305</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2085; 9145</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2495; 10645</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>6890; 18318</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3225</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4392</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>4209</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>5871</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>3191</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2296</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>9095</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>7582</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1281; 7008</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1820; 7919</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1745; 7299</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2792; 9966</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>750; 7239</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>686; 5782</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3509</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>5300; 14404</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>4313; 12599</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3489; 10746</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3212</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>11155</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>14895</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>15013</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>20465</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>16058</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>9798</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>25837</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>46840</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>30953</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>24812</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>6445; 17141</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>18949; 34234</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>9846; 21561</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>8044; 25937</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>9792; 21384</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>13999; 28216</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>10193; 23328</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>5777; 17076</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>18490; 34483</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>37430; 58313</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>23748; 40852</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>16992; 35777</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,92</t>
+          <t>0,0; 29,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,79; 50,54</t>
+          <t>11,12; 50,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,5</t>
+          <t>0,0; 15,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 43,39</t>
+          <t>2,82; 44,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 40,3</t>
+          <t>5,15; 40,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 30,63</t>
+          <t>3,3; 32,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,99; 34,4</t>
+          <t>5,88; 35,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 8,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 28,27</t>
+          <t>4,74; 26,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,65; 34,86</t>
+          <t>9,98; 33,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 20,83</t>
+          <t>4,48; 21,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 28,9</t>
+          <t>2,73; 26,89</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,86</t>
+          <t>0,0; 21,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 22,86</t>
+          <t>2,65; 22,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 17,96</t>
+          <t>2,05; 17,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,64</t>
+          <t>0,0; 7,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,03</t>
+          <t>0,0; 16,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 23,47</t>
+          <t>2,63; 24,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,3; 51,03</t>
+          <t>18,62; 49,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 9,87</t>
+          <t>0,81; 8,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 13,42</t>
+          <t>1,55; 13,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 18,83</t>
+          <t>4,1; 18,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,78; 26,95</t>
+          <t>10,61; 27,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 6,11</t>
+          <t>0,36; 5,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,94</t>
+          <t>0,0; 29,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,29; 52,49</t>
+          <t>13,65; 52,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 54,94</t>
+          <t>6,98; 53,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,51</t>
+          <t>0,0; 12,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,84</t>
+          <t>0,0; 26,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 35,44</t>
+          <t>6,46; 34,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,79</t>
+          <t>0,0; 38,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,29</t>
+          <t>0,0; 13,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,64</t>
+          <t>0,0; 20,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,3; 36,87</t>
+          <t>13,11; 35,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 36,5</t>
+          <t>3,78; 33,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,42</t>
+          <t>0,0; 10,17</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,41</t>
+          <t>0,0; 23,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 32,99</t>
+          <t>3,23; 30,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 33,69</t>
+          <t>7,31; 32,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,42 +1157,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 38,21</t>
+          <t>4,19; 37,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,61; 42,58</t>
+          <t>5,69; 43,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 22,12</t>
+          <t>2,63; 20,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,64</t>
+          <t>0,0; 49,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 22,51</t>
+          <t>4,01; 22,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,58; 29,86</t>
+          <t>7,87; 30,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 22,02</t>
+          <t>6,45; 21,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,31</t>
+          <t>0,0; 28,13</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,43; 54,11</t>
+          <t>10,45; 53,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,04</t>
+          <t>0,0; 52,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,46</t>
+          <t>0,0; 38,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,32</t>
+          <t>0,0; 23,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,02; 33,43</t>
+          <t>8,07; 35,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,23</t>
+          <t>0,0; 33,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,54</t>
+          <t>0,0; 20,76</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,87</t>
+          <t>0,0; 23,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,68</t>
+          <t>0,0; 35,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,94</t>
+          <t>0,0; 33,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,88</t>
+          <t>0,0; 37,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,16</t>
+          <t>0,0; 35,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 30,18</t>
+          <t>3,99; 32,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,25</t>
+          <t>0,0; 48,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,18</t>
+          <t>0,0; 28,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 22,37</t>
+          <t>2,67; 22,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,01; 25,87</t>
+          <t>5,04; 26,59</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,73</t>
+          <t>0,0; 29,72</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,85</t>
+          <t>0,0; 20,6</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,09; 29,95</t>
+          <t>6,03; 32,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 24,98</t>
+          <t>2,62; 24,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,44; 38,44</t>
+          <t>13,43; 36,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,33</t>
+          <t>0,0; 18,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 24,37</t>
+          <t>2,53; 27,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,52; 20,98</t>
+          <t>3,91; 21,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,34; 19,04</t>
+          <t>4,17; 19,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 20,51</t>
+          <t>4,46; 19,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,29; 24,71</t>
+          <t>9,25; 23,82</t>
         </is>
       </c>
     </row>
@@ -1697,17 +1697,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,94; 27,03</t>
+          <t>4,96; 25,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,57; 37,31</t>
+          <t>9,01; 38,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,34; 34,89</t>
+          <t>9,14; 35,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,42 +1717,42 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,0; 25,0</t>
+          <t>7,9; 26,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,46; 33,37</t>
+          <t>3,6; 35,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 23,12</t>
+          <t>2,8; 23,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,98</t>
+          <t>0,0; 31,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,06; 21,89</t>
+          <t>7,71; 20,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,05; 29,36</t>
+          <t>9,64; 29,49</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,6; 23,4</t>
+          <t>7,47; 24,24</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,21</t>
+          <t>0,0; 17,16</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 13,68</t>
+          <t>5,27; 13,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,83; 23,18</t>
+          <t>12,97; 23,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,72; 16,92</t>
+          <t>7,5; 16,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,59</t>
+          <t>4,49; 14,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,8; 14,86</t>
+          <t>6,59; 14,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,86; 17,86</t>
+          <t>9,09; 18,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,27; 18,92</t>
+          <t>8,47; 19,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 9,37</t>
+          <t>2,99; 9,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,87; 12,81</t>
+          <t>6,53; 12,76</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12,25; 19,08</t>
+          <t>12,03; 19,24</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9,47; 16,29</t>
+          <t>9,13; 16,05</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,94</t>
+          <t>4,51; 10,02</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3608</t>
+          <t>0; 3496</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1736; 8133</t>
+          <t>1790; 8090</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2333</t>
+          <t>0; 2545</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>851; 13183</t>
+          <t>856; 13437</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>636; 4891</t>
+          <t>625; 4900</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>584; 5521</t>
+          <t>594; 5910</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1151; 6607</t>
+          <t>1130; 6746</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2178</t>
+          <t>0; 1865</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1118; 6729</t>
+          <t>1128; 6382</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3292; 11894</t>
+          <t>3404; 11264</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1605; 7351</t>
+          <t>1582; 7611</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1329; 15233</t>
+          <t>1438; 14173</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4159</t>
+          <t>0; 3620</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>610; 5369</t>
+          <t>623; 5255</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>563; 4897</t>
+          <t>558; 4761</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4186</t>
+          <t>0; 4519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3182</t>
+          <t>0; 3322</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>651; 5862</t>
+          <t>657; 6111</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3578; 10555</t>
+          <t>3851; 10166</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>398; 4754</t>
+          <t>390; 4245</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>568; 4909</t>
+          <t>568; 4928</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1980; 9126</t>
+          <t>1985; 8801</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4690; 12921</t>
+          <t>5087; 13324</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>492; 6796</t>
+          <t>404; 6596</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2784</t>
+          <t>0; 3469</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2064; 8152</t>
+          <t>2120; 8225</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>665; 5232</t>
+          <t>665; 5119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1885</t>
+          <t>0; 2204</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3152</t>
+          <t>0; 2842</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1408; 7906</t>
+          <t>1442; 7667</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>0; 3211</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0; 2735</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3507</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3914</t>
+          <t>0; 4517</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5032; 13950</t>
+          <t>4960; 13372</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1304; 6519</t>
+          <t>676; 6045</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3602</t>
+          <t>0; 3888</t>
         </is>
       </c>
     </row>
@@ -2833,17 +2833,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3665</t>
+          <t>0; 3923</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>844; 6373</t>
+          <t>624; 5864</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1941; 8018</t>
+          <t>1741; 7725</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,42 +2853,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>684; 6276</t>
+          <t>689; 6235</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>855; 6489</t>
+          <t>868; 6665</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>674; 5659</t>
+          <t>673; 5364</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5718</t>
+          <t>0; 5523</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1319; 7379</t>
+          <t>1313; 7456</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2621; 10320</t>
+          <t>2719; 10393</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3300; 10873</t>
+          <t>3184; 10627</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 6208</t>
+          <t>0; 6637</t>
         </is>
       </c>
     </row>
@@ -3046,17 +3046,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1514; 7850</t>
+          <t>1516; 7711</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3388</t>
+          <t>0; 3394</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3333</t>
+          <t>0; 3179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2865</t>
+          <t>0; 2878</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2150; 8958</t>
+          <t>2163; 9424</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3764</t>
+          <t>0; 3869</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3319</t>
+          <t>0; 3928</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3574</t>
+          <t>0; 2885</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5239</t>
+          <t>0; 3911</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3637</t>
+          <t>0; 3029</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2986</t>
+          <t>0; 2888</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3772</t>
+          <t>0; 3851</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>702; 5460</t>
+          <t>721; 5894</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4364</t>
+          <t>0; 4193</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3699</t>
+          <t>0; 3905</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>612; 5170</t>
+          <t>617; 5303</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1456; 7524</t>
+          <t>1465; 7732</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5290</t>
+          <t>0; 5287</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4439</t>
+          <t>0; 4386</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1310; 6438</t>
+          <t>1297; 6933</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>691; 6636</t>
+          <t>696; 6491</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3472,17 +3472,17 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4003; 11450</t>
+          <t>4001; 10890</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4332</t>
+          <t>0; 4992</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>640; 6177</t>
+          <t>641; 6846</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3492,17 +3492,17 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1563; 9305</t>
+          <t>1734; 9607</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2085; 9145</t>
+          <t>2003; 9266</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2495; 10645</t>
+          <t>2317; 10124</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6890; 18318</t>
+          <t>6856; 17659</t>
         </is>
       </c>
     </row>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1281; 7008</t>
+          <t>1285; 6618</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1820; 7919</t>
+          <t>1912; 8107</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1745; 7299</t>
+          <t>1911; 7505</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,42 +3685,42 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2792; 9966</t>
+          <t>3149; 10429</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>750; 7239</t>
+          <t>780; 7728</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>686; 5782</t>
+          <t>700; 5960</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 3509</t>
+          <t>0; 3672</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5300; 14404</t>
+          <t>5074; 13752</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4313; 12599</t>
+          <t>4139; 12655</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3489; 10746</t>
+          <t>3433; 11133</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 3212</t>
+          <t>0; 3401</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>6445; 17141</t>
+          <t>6600; 17356</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>18949; 34234</t>
+          <t>19150; 34373</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9846; 21561</t>
+          <t>9561; 20678</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8044; 25937</t>
+          <t>7984; 25286</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>9792; 21384</t>
+          <t>9481; 20949</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13999; 28216</t>
+          <t>14362; 29524</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10193; 23328</t>
+          <t>10447; 23916</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5777; 17076</t>
+          <t>5454; 16563</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18490; 34483</t>
+          <t>17591; 34355</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37430; 58313</t>
+          <t>36772; 58807</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23748; 40852</t>
+          <t>22883; 40249</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16992; 35777</t>
+          <t>16231; 36075</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17,08%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9,56%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>27,8%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,91%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16,76%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,96</t>
+          <t>5,27; 39,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,12; 50,27</t>
+          <t>3,3; 30,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,81</t>
+          <t>5,86; 35,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 44,22</t>
+          <t>0,0; 11,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 40,38</t>
+          <t>0,0; 29,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 32,79</t>
+          <t>12,48; 49,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 35,12</t>
+          <t>0,0; 16,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,36</t>
+          <t>2,43; 22,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 26,81</t>
+          <t>4,94; 26,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 33,02</t>
+          <t>9,29; 34,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 21,56</t>
+          <t>4,35; 22,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 26,89</t>
+          <t>2,03; 12,85</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,59%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32,26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>7,06%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,51%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>6,52%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>32,26%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,64</t>
+          <t>0,0; 13,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 22,38</t>
+          <t>2,63; 24,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 17,46</t>
+          <t>16,7; 49,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,17</t>
+          <t>0,67; 8,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,73</t>
+          <t>0,0; 24,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 24,47</t>
+          <t>2,64; 21,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,62; 49,15</t>
+          <t>2,1; 18,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,81</t>
+          <t>0,0; 7,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 13,47</t>
+          <t>0,24; 13,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 18,16</t>
+          <t>4,14; 18,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,61; 27,79</t>
+          <t>9,28; 26,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,93</t>
+          <t>0,42; 6,63</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,64%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>28,98%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>23,32%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,84</t>
+          <t>0,0; 27,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,65; 52,96</t>
+          <t>8,85; 34,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 53,76</t>
+          <t>0,0; 32,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,29</t>
+          <t>0,0; 18,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,91</t>
+          <t>0,0; 23,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 34,37</t>
+          <t>10,35; 51,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,51</t>
+          <t>6,95; 52,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,48</t>
+          <t>0,0; 11,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,36</t>
+          <t>0,0; 18,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,11; 35,34</t>
+          <t>12,84; 36,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 33,84</t>
+          <t>4,03; 35,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,17</t>
+          <t>0,0; 11,18</t>
         </is>
       </c>
     </row>
@@ -1069,49 +1069,49 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19,95%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11,03%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,78%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,44%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>18,01%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,95%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10,87%</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>16,31%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,99</t>
+          <t>4,47; 37,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 30,35</t>
+          <t>6,02; 45,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 32,46</t>
+          <t>2,56; 22,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 47,97</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 23,79</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,38; 30,88</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7,68; 32,13</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4,19; 37,96</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,69; 43,73</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,63; 20,97</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 49,88</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 22,75</t>
+          <t>4,22; 24,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 30,07</t>
+          <t>7,9; 28,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 21,52</t>
+          <t>6,7; 23,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,13</t>
+          <t>0,0; 23,48</t>
         </is>
       </c>
     </row>
@@ -1214,44 +1214,44 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>27,39%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>18,34%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>14,09%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>17,43%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,45; 53,15</t>
+          <t>0,0; 23,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,37 +1302,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,42</t>
+          <t>10,54; 54,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 53,7</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 41,23</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 35,17</t>
+          <t>6,03; 31,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,12</t>
+          <t>0,0; 32,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,76</t>
+          <t>0,0; 21,3</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12,29%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11,24%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5,73%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>13,49%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8,11%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11,24%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,31</t>
+          <t>0,0; 35,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,6</t>
+          <t>0,0; 28,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,27</t>
+          <t>0,0; 52,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,61</t>
+          <t>0,0; 29,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,89</t>
+          <t>0,0; 30,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,99; 32,57</t>
+          <t>0,0; 42,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,28</t>
+          <t>0,0; 38,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,7</t>
+          <t>0,0; 30,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,67; 22,95</t>
+          <t>2,64; 22,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,04; 26,59</t>
+          <t>2,67; 25,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,72</t>
+          <t>0,0; 30,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,6</t>
+          <t>0,0; 19,03</t>
         </is>
       </c>
     </row>
@@ -1489,62 +1489,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>16,16%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>11,14%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24,43%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10,0%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10,36%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 32,25</t>
+          <t>0,0; 16,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 24,44</t>
+          <t>2,5; 24,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,43; 36,56</t>
+          <t>3,56; 21,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,82</t>
+          <t>6,33; 32,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 27,01</t>
+          <t>2,62; 25,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,91; 21,66</t>
+          <t>12,42; 37,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 19,29</t>
+          <t>4,51; 20,21</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,46; 19,51</t>
+          <t>4,27; 20,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,25; 23,82</t>
+          <t>9,36; 25,25</t>
         </is>
       </c>
     </row>
@@ -1629,44 +1629,44 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>14,73%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>12,44%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>20,69%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>20,12%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>14,73%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t>13,82%</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,96; 25,53</t>
+          <t>6,9; 24,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,01; 38,2</t>
+          <t>3,87; 34,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,14; 35,88</t>
+          <t>2,82; 24,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>0,0; 21,38</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4,94; 24,83</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8,96; 36,69</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,6; 35,77</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>7,9; 26,16</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3,6; 35,63</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,8; 23,83</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 31,37</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,71; 20,9</t>
+          <t>8,34; 21,84</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,64; 29,49</t>
+          <t>9,58; 28,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,47; 24,24</t>
+          <t>7,81; 24,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,16</t>
+          <t>0,0; 13,47</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>8,9%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>17,86%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>11,69%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,27; 13,85</t>
+          <t>6,49; 15,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,97; 23,27</t>
+          <t>8,82; 18,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,5; 16,22</t>
+          <t>8,73; 18,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,49; 14,23</t>
+          <t>2,82; 9,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,59; 14,56</t>
+          <t>5,51; 13,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,09; 18,69</t>
+          <t>12,88; 23,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,47; 19,4</t>
+          <t>7,52; 16,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,09</t>
+          <t>5,36; 12,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,53; 12,76</t>
+          <t>6,83; 12,52</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12,03; 19,24</t>
+          <t>12,25; 19,17</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9,13; 16,05</t>
+          <t>9,44; 16,06</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 10,02</t>
+          <t>4,6; 9,34</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1115</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4474</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>469</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2090</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3280</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>2333</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3496</t>
+          <t>640; 4832</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1790; 8090</t>
+          <t>595; 5580</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2545</t>
+          <t>1126; 6887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>856; 13437</t>
+          <t>0; 2247</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>625; 4900</t>
+          <t>0; 3447</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>594; 5910</t>
+          <t>2008; 8014</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1130; 6746</t>
+          <t>0; 2691</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1865</t>
+          <t>505; 4694</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1128; 6382</t>
+          <t>1176; 6305</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3404; 11264</t>
+          <t>3170; 11659</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1582; 7611</t>
+          <t>1534; 7975</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1438; 14173</t>
+          <t>814; 5150</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6673</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1182</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1997</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1778</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6673</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>690</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>1915</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3620</t>
+          <t>0; 2651</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>623; 5255</t>
+          <t>657; 6018</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>558; 4761</t>
+          <t>3455; 10308</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4519</t>
+          <t>286; 3505</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3322</t>
+          <t>0; 4089</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>657; 6111</t>
+          <t>620; 4974</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3851; 10166</t>
+          <t>572; 4908</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>390; 4245</t>
+          <t>0; 3047</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>568; 4928</t>
+          <t>89; 5019</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1985; 8801</t>
+          <t>2008; 8811</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5087; 13324</t>
+          <t>4449; 12832</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>404; 6596</t>
+          <t>345; 5401</t>
         </is>
       </c>
     </row>
@@ -2499,27 +2499,27 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4159</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2221</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4159</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>354</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>963</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3469</t>
+          <t>0; 2913</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2120; 8225</t>
+          <t>1975; 7805</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>665; 5119</t>
+          <t>0; 2747</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2204</t>
+          <t>0; 3189</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2842</t>
+          <t>0; 2778</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1442; 7667</t>
+          <t>1607; 7987</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3211</t>
+          <t>662; 4965</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2735</t>
+          <t>0; 1897</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4517</t>
+          <t>0; 4023</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4960; 13372</t>
+          <t>4857; 13654</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>676; 6045</t>
+          <t>721; 6355</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3888</t>
+          <t>0; 3898</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,44 +2765,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2783</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2168</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1149</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>781</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2597</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4286</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2783</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2168</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>3564</t>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1149</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3923</t>
+          <t>734; 6115</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>624; 5864</t>
+          <t>918; 6925</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1741; 7725</t>
+          <t>655; 5774</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>0; 4997</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3891</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>653; 5965</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1829; 7645</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>689; 6235</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>868; 6665</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>673; 5364</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0; 5523</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1313; 7456</t>
+          <t>1383; 8012</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2719; 10393</t>
+          <t>2732; 9976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3184; 10627</t>
+          <t>3308; 11472</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 6637</t>
+          <t>0; 5316</t>
         </is>
       </c>
     </row>
@@ -2910,37 +2910,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2978,44 +2978,44 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>3974</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>1194</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1189</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t>4671</t>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1189</t>
         </is>
       </c>
     </row>
@@ -3046,17 +3046,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1516; 7711</t>
+          <t>0; 2936</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3394</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3179</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,37 +3066,37 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2878</t>
+          <t>1529; 7876</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>0; 3497</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3479</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2163; 9424</t>
+          <t>1616; 8473</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3869</t>
+          <t>0; 3779</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3928</t>
+          <t>0; 3872</t>
         </is>
       </c>
     </row>
@@ -3113,32 +3113,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2224</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>709</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1483</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1272</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2224</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>571</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1288</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2885</t>
+          <t>0; 3811</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3911</t>
+          <t>0; 5221</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3029</t>
+          <t>0; 4535</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2888</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3851</t>
+          <t>0; 3805</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>721; 5894</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4193</t>
+          <t>0; 3529</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3905</t>
+          <t>0; 2352</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>617; 5303</t>
+          <t>610; 5199</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1465; 7732</t>
+          <t>775; 7414</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5287</t>
+          <t>0; 5508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4386</t>
+          <t>0; 3634</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,62 +3389,62 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>3474</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2958</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>7278</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1445</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2419</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>7114</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>5377</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>4919</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>5377</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>11430</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1297; 6933</t>
+          <t>0; 4310</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>696; 6491</t>
+          <t>635; 6112</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3472,17 +3472,17 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4001; 10890</t>
+          <t>1498; 9111</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4992</t>
+          <t>1362; 7038</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>641; 6846</t>
+          <t>696; 6731</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3492,17 +3492,17 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1734; 9607</t>
+          <t>3760; 11451</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2003; 9266</t>
+          <t>2165; 9706</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2317; 10124</t>
+          <t>2217; 10550</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6856; 17659</t>
+          <t>6768; 18257</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,44 +3597,44 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5871</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3191</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2296</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>3225</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>4392</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>4209</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>5871</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>3191</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>9095</t>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>579</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1285; 6618</t>
+          <t>2751; 9842</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1912; 8107</t>
+          <t>840; 7376</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1911; 7505</t>
+          <t>706; 6223</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
+          <t>0; 2503</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1280; 6437</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1902; 7787</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1799; 7482</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>3149; 10429</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>780; 7728</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>700; 5960</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0; 3672</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5074; 13752</t>
+          <t>5490; 14366</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4139; 12655</t>
+          <t>4111; 12295</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3433; 11133</t>
+          <t>3589; 11104</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 3401</t>
+          <t>0; 2604</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>20465</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>16058</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>8935</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>11155</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>26375</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>14895</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>15013</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>14682</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>20465</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>16058</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>20846</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>6600; 17356</t>
+          <t>9344; 21724</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>19150; 34373</t>
+          <t>13930; 28618</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9561; 20678</t>
+          <t>10764; 23141</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7984; 25286</t>
+          <t>4658; 15696</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>9481; 20949</t>
+          <t>6900; 17203</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14362; 29524</t>
+          <t>19018; 35328</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10447; 23916</t>
+          <t>9591; 21149</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5454; 16563</t>
+          <t>7662; 18239</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17591; 34355</t>
+          <t>18380; 33703</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36772; 58807</t>
+          <t>37446; 58597</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22883; 40249</t>
+          <t>23666; 40267</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16231; 36075</t>
+          <t>14164; 28753</t>
         </is>
       </c>
     </row>
